--- a/Data/Building/Lab.Curtain002.xlsx
+++ b/Data/Building/Lab.Curtain002.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709252395</v>
+        <v>1711844284</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -505,6 +510,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
